--- a/data/mappings/product_names.xlsx
+++ b/data/mappings/product_names.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jalil Shojazade\Desktop\Luxbaz_product_import\4_Product_import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Luxbaz\All Codes\Projects\product-import-pipeline\data\mappings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3266AFC6-B253-4159-8685-0C5F679D3240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14ED41D3-99E5-4013-B3ED-046120A6A399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="81">
   <si>
     <t>Persian</t>
   </si>
@@ -263,12 +263,6 @@
   </si>
   <si>
     <t>men-waist-bag</t>
-  </si>
-  <si>
-    <t>کیف پاسپورتی 4735</t>
-  </si>
-  <si>
-    <t>کیف زنانه 5731</t>
   </si>
 </sst>
 </file>
@@ -612,6 +606,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -955,7 +950,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
         <v>62</v>
@@ -963,7 +958,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="B44" t="s">
         <v>66</v>
